--- a/excel_routes/route_DMM_HMB_threats.xlsx
+++ b/excel_routes/route_DMM_HMB_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC2B68D-3468-4774-A14A-4D983458693F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA60C89F-AF23-4DA8-883F-03DCEFE919AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="44">
   <si>
     <t>Date</t>
   </si>
@@ -60,39 +60,39 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>27-JUL-26</t>
+    <t>31-JUL-26</t>
   </si>
   <si>
     <t>SM-438</t>
   </si>
   <si>
+    <t>Nesma Airlines NE-151</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>Nile Air NP-232</t>
+  </si>
+  <si>
+    <t>03-AUG-26</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>Nile Air NP-332</t>
   </si>
   <si>
     <t>MED</t>
   </si>
   <si>
-    <t>SAR</t>
-  </si>
-  <si>
     <t>Nile Air NP-334</t>
   </si>
   <si>
-    <t>Nesma Airlines NE-151</t>
-  </si>
-  <si>
-    <t>31-JUL-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-232</t>
-  </si>
-  <si>
-    <t>03-AUG-26</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
     <t>07-AUG-26</t>
   </si>
   <si>
@@ -105,34 +105,34 @@
     <t>10-AUG-26</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>14-AUG-26</t>
   </si>
   <si>
+    <t>EgyptAir MS-698</t>
+  </si>
+  <si>
     <t>17-AUG-26</t>
   </si>
   <si>
+    <t>21-AUG-26</t>
+  </si>
+  <si>
+    <t>24-AUG-26</t>
+  </si>
+  <si>
+    <t>28-AUG-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-155</t>
+  </si>
+  <si>
+    <t>31-AUG-26</t>
+  </si>
+  <si>
+    <t>04-SEP-26</t>
+  </si>
+  <si>
     <t>flynas XY-894</t>
-  </si>
-  <si>
-    <t>21-AUG-26</t>
-  </si>
-  <si>
-    <t>24-AUG-26</t>
-  </si>
-  <si>
-    <t>28-AUG-26</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-155</t>
-  </si>
-  <si>
-    <t>31-AUG-26</t>
-  </si>
-  <si>
-    <t>04-SEP-26</t>
   </si>
   <si>
     <t>flyadeal F3-911</t>
@@ -198,8 +198,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFFFF3CD"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -210,8 +210,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -562,7 +562,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>353</v>
+        <v>420</v>
       </c>
       <c r="E2" s="2">
         <v>669</v>
       </c>
       <c r="F2" s="2">
-        <v>-316</v>
+        <v>-249</v>
       </c>
       <c r="G2" s="2">
         <v>40</v>
@@ -658,13 +658,13 @@
         <v>16</v>
       </c>
       <c r="D3" s="2">
-        <v>353</v>
+        <v>421</v>
       </c>
       <c r="E3" s="2">
         <v>669</v>
       </c>
       <c r="F3" s="2">
-        <v>-316</v>
+        <v>-248</v>
       </c>
       <c r="G3" s="2">
         <v>40</v>
@@ -684,22 +684,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="E4" s="2">
-        <v>669</v>
+        <v>831</v>
       </c>
       <c r="F4" s="2">
-        <v>-310</v>
+        <v>-480</v>
       </c>
       <c r="G4" s="2">
         <v>40</v>
@@ -710,8 +710,8 @@
       <c r="I4" s="2">
         <v>-10</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>14</v>
+      <c r="J4" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>15</v>
@@ -719,22 +719,22 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E5" s="2">
-        <v>750</v>
+        <v>831</v>
       </c>
       <c r="F5" s="2">
-        <v>-391</v>
+        <v>-410</v>
       </c>
       <c r="G5" s="2">
         <v>40</v>
@@ -745,8 +745,8 @@
       <c r="I5" s="2">
         <v>-10</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>14</v>
+      <c r="J5" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -754,22 +754,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2">
         <v>421</v>
       </c>
       <c r="E6" s="2">
-        <v>750</v>
+        <v>831</v>
       </c>
       <c r="F6" s="2">
-        <v>-329</v>
+        <v>-410</v>
       </c>
       <c r="G6" s="2">
         <v>40</v>
@@ -780,8 +780,8 @@
       <c r="I6" s="2">
         <v>-10</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>14</v>
+      <c r="J6" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>15</v>
@@ -789,22 +789,22 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D7" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="E7" s="2">
         <v>831</v>
       </c>
       <c r="F7" s="2">
-        <v>-472</v>
+        <v>-480</v>
       </c>
       <c r="G7" s="2">
         <v>40</v>
@@ -816,7 +816,7 @@
         <v>-10</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -833,13 +833,13 @@
         <v>13</v>
       </c>
       <c r="D8" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E8" s="2">
         <v>831</v>
       </c>
       <c r="F8" s="2">
-        <v>-410</v>
+        <v>-480</v>
       </c>
       <c r="G8" s="2">
         <v>40</v>
@@ -850,8 +850,8 @@
       <c r="I8" s="2">
         <v>-10</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>14</v>
+      <c r="J8" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2">
-        <v>421</v>
+        <v>353</v>
       </c>
       <c r="E9" s="2">
         <v>831</v>
       </c>
       <c r="F9" s="2">
-        <v>-410</v>
+        <v>-478</v>
       </c>
       <c r="G9" s="2">
         <v>40</v>
@@ -885,8 +885,8 @@
       <c r="I9" s="2">
         <v>-10</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>14</v>
+      <c r="J9" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -894,22 +894,22 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D10" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E10" s="2">
-        <v>831</v>
+        <v>507</v>
       </c>
       <c r="F10" s="2">
-        <v>-472</v>
+        <v>-86</v>
       </c>
       <c r="G10" s="2">
         <v>40</v>
@@ -920,8 +920,8 @@
       <c r="I10" s="2">
         <v>-10</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>21</v>
+      <c r="J10" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -929,22 +929,22 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E11" s="2">
-        <v>831</v>
+        <v>750</v>
       </c>
       <c r="F11" s="2">
-        <v>-472</v>
+        <v>-329</v>
       </c>
       <c r="G11" s="2">
         <v>40</v>
@@ -955,8 +955,8 @@
       <c r="I11" s="2">
         <v>-10</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>21</v>
+      <c r="J11" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -964,22 +964,22 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2">
         <v>421</v>
       </c>
       <c r="E12" s="2">
-        <v>831</v>
+        <v>750</v>
       </c>
       <c r="F12" s="2">
-        <v>-410</v>
+        <v>-329</v>
       </c>
       <c r="G12" s="2">
         <v>40</v>
@@ -990,8 +990,8 @@
       <c r="I12" s="2">
         <v>-10</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>14</v>
+      <c r="J12" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -999,34 +999,34 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D13" s="2">
-        <v>421</v>
+        <v>773</v>
       </c>
       <c r="E13" s="2">
-        <v>561</v>
+        <v>750</v>
       </c>
       <c r="F13" s="2">
-        <v>-140</v>
+        <v>23</v>
       </c>
       <c r="G13" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2">
         <v>30</v>
       </c>
       <c r="I13" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>26</v>
+        <v>-16</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -1034,22 +1034,22 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="E14" s="2">
-        <v>750</v>
+        <v>615</v>
       </c>
       <c r="F14" s="2">
-        <v>-329</v>
+        <v>-264</v>
       </c>
       <c r="G14" s="2">
         <v>40</v>
@@ -1060,8 +1060,8 @@
       <c r="I14" s="2">
         <v>-10</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>14</v>
+      <c r="J14" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1069,7 +1069,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1081,10 +1081,10 @@
         <v>421</v>
       </c>
       <c r="E15" s="2">
-        <v>750</v>
+        <v>615</v>
       </c>
       <c r="F15" s="2">
-        <v>-329</v>
+        <v>-194</v>
       </c>
       <c r="G15" s="2">
         <v>40</v>
@@ -1104,22 +1104,22 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="2">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E16" s="2">
-        <v>912</v>
+        <v>615</v>
       </c>
       <c r="F16" s="2">
-        <v>-553</v>
+        <v>-194</v>
       </c>
       <c r="G16" s="2">
         <v>40</v>
@@ -1130,8 +1130,8 @@
       <c r="I16" s="2">
         <v>-10</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>21</v>
+      <c r="J16" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>15</v>
@@ -1139,22 +1139,22 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D17" s="2">
         <v>421</v>
       </c>
       <c r="E17" s="2">
-        <v>912</v>
+        <v>615</v>
       </c>
       <c r="F17" s="2">
-        <v>-491</v>
+        <v>-194</v>
       </c>
       <c r="G17" s="2">
         <v>40</v>
@@ -1165,8 +1165,8 @@
       <c r="I17" s="2">
         <v>-10</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>21</v>
+      <c r="J17" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>15</v>
@@ -1174,22 +1174,22 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2">
-        <v>584</v>
+        <v>351</v>
       </c>
       <c r="E18" s="2">
         <v>912</v>
       </c>
       <c r="F18" s="2">
-        <v>-328</v>
+        <v>-561</v>
       </c>
       <c r="G18" s="2">
         <v>40</v>
@@ -1200,8 +1200,8 @@
       <c r="I18" s="2">
         <v>-10</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>14</v>
+      <c r="J18" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>15</v>
@@ -1215,16 +1215,16 @@
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E19" s="2">
-        <v>615</v>
+        <v>912</v>
       </c>
       <c r="F19" s="2">
-        <v>-194</v>
+        <v>-492</v>
       </c>
       <c r="G19" s="2">
         <v>40</v>
@@ -1235,8 +1235,8 @@
       <c r="I19" s="2">
         <v>-10</v>
       </c>
-      <c r="J19" s="5" t="s">
-        <v>26</v>
+      <c r="J19" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>15</v>
@@ -1256,10 +1256,10 @@
         <v>421</v>
       </c>
       <c r="E20" s="2">
-        <v>615</v>
+        <v>912</v>
       </c>
       <c r="F20" s="2">
-        <v>-194</v>
+        <v>-491</v>
       </c>
       <c r="G20" s="2">
         <v>40</v>
@@ -1270,8 +1270,8 @@
       <c r="I20" s="2">
         <v>-10</v>
       </c>
-      <c r="J20" s="5" t="s">
-        <v>26</v>
+      <c r="J20" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1285,16 +1285,16 @@
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D21" s="2">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="E21" s="2">
         <v>912</v>
       </c>
       <c r="F21" s="2">
-        <v>-553</v>
+        <v>-492</v>
       </c>
       <c r="G21" s="2">
         <v>40</v>
@@ -1306,7 +1306,7 @@
         <v>-10</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>15</v>
@@ -1320,16 +1320,16 @@
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D22" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E22" s="2">
         <v>912</v>
       </c>
       <c r="F22" s="2">
-        <v>-492</v>
+        <v>-491</v>
       </c>
       <c r="G22" s="2">
         <v>40</v>
@@ -1341,7 +1341,7 @@
         <v>-10</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>15</v>
@@ -1355,7 +1355,7 @@
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2">
         <v>421</v>
@@ -1376,7 +1376,7 @@
         <v>-10</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>15</v>
@@ -1384,22 +1384,22 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D24" s="2">
         <v>420</v>
       </c>
       <c r="E24" s="2">
-        <v>912</v>
+        <v>1020</v>
       </c>
       <c r="F24" s="2">
-        <v>-492</v>
+        <v>-600</v>
       </c>
       <c r="G24" s="2">
         <v>40</v>
@@ -1411,7 +1411,7 @@
         <v>-10</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>15</v>
@@ -1419,22 +1419,22 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E25" s="2">
-        <v>912</v>
+        <v>1020</v>
       </c>
       <c r="F25" s="2">
-        <v>-491</v>
+        <v>-600</v>
       </c>
       <c r="G25" s="2">
         <v>40</v>
@@ -1446,7 +1446,7 @@
         <v>-10</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>15</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1466,10 +1466,10 @@
         <v>421</v>
       </c>
       <c r="E26" s="2">
-        <v>912</v>
+        <v>1020</v>
       </c>
       <c r="F26" s="2">
-        <v>-491</v>
+        <v>-599</v>
       </c>
       <c r="G26" s="2">
         <v>40</v>
@@ -1481,7 +1481,7 @@
         <v>-10</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>15</v>
@@ -1495,28 +1495,28 @@
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D27" s="2">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2">
-        <v>1020</v>
+        <v>1753</v>
       </c>
       <c r="F27" s="2">
-        <v>-600</v>
+        <v>-1384</v>
       </c>
       <c r="G27" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2">
         <v>30</v>
       </c>
       <c r="I27" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>15</v>
@@ -1530,28 +1530,28 @@
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D28" s="2">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="E28" s="2">
-        <v>1020</v>
+        <v>1753</v>
       </c>
       <c r="F28" s="2">
-        <v>-600</v>
+        <v>-1364</v>
       </c>
       <c r="G28" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2">
         <v>30</v>
       </c>
       <c r="I28" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>15</v>
@@ -1565,28 +1565,28 @@
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D29" s="2">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="E29" s="2">
-        <v>1020</v>
+        <v>1753</v>
       </c>
       <c r="F29" s="2">
-        <v>-599</v>
+        <v>-1288</v>
       </c>
       <c r="G29" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H29" s="2">
         <v>30</v>
       </c>
       <c r="I29" s="2">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>15</v>
@@ -1594,22 +1594,22 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D30" s="2">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="E30" s="2">
         <v>1753</v>
       </c>
       <c r="F30" s="2">
-        <v>-1364</v>
+        <v>-1384</v>
       </c>
       <c r="G30" s="2">
         <v>15</v>
@@ -1621,7 +1621,7 @@
         <v>15</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>15</v>
@@ -1629,34 +1629,34 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D31" s="2">
-        <v>614</v>
+        <v>559</v>
       </c>
       <c r="E31" s="2">
         <v>1753</v>
       </c>
       <c r="F31" s="2">
-        <v>-1139</v>
+        <v>-1194</v>
       </c>
       <c r="G31" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2">
         <v>30</v>
       </c>
       <c r="I31" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>15</v>
@@ -1664,34 +1664,34 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D32" s="2">
-        <v>693</v>
+        <v>626</v>
       </c>
       <c r="E32" s="2">
         <v>1753</v>
       </c>
       <c r="F32" s="2">
-        <v>-1060</v>
+        <v>-1127</v>
       </c>
       <c r="G32" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2">
         <v>30</v>
       </c>
       <c r="I32" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>15</v>
@@ -1699,7 +1699,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>12</v>
@@ -1726,7 +1726,7 @@
         <v>15</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>15</v>
@@ -1734,34 +1734,34 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D34" s="2">
-        <v>419</v>
+        <v>465</v>
       </c>
       <c r="E34" s="2">
         <v>1753</v>
       </c>
       <c r="F34" s="2">
-        <v>-1334</v>
+        <v>-1288</v>
       </c>
       <c r="G34" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2">
         <v>30</v>
       </c>
       <c r="I34" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>15</v>
@@ -1769,34 +1769,34 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D35" s="2">
-        <v>626</v>
+        <v>564</v>
       </c>
       <c r="E35" s="2">
         <v>1753</v>
       </c>
       <c r="F35" s="2">
-        <v>-1127</v>
+        <v>-1189</v>
       </c>
       <c r="G35" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H35" s="2">
         <v>30</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1804,34 +1804,34 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D36" s="2">
-        <v>467</v>
+        <v>369</v>
       </c>
       <c r="E36" s="2">
         <v>1753</v>
       </c>
       <c r="F36" s="2">
-        <v>-1286</v>
+        <v>-1384</v>
       </c>
       <c r="G36" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H36" s="2">
         <v>30</v>
       </c>
       <c r="I36" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>15</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>12</v>
@@ -1848,25 +1848,25 @@
         <v>36</v>
       </c>
       <c r="D37" s="2">
-        <v>559</v>
+        <v>389</v>
       </c>
       <c r="E37" s="2">
         <v>1753</v>
       </c>
       <c r="F37" s="2">
-        <v>-1194</v>
+        <v>-1364</v>
       </c>
       <c r="G37" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2">
         <v>30</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>15</v>
@@ -1874,34 +1874,34 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D38" s="2">
-        <v>614</v>
+        <v>686</v>
       </c>
       <c r="E38" s="2">
         <v>1753</v>
       </c>
       <c r="F38" s="2">
-        <v>-1139</v>
+        <v>-1067</v>
       </c>
       <c r="G38" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H38" s="2">
         <v>30</v>
       </c>
       <c r="I38" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>15</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>12</v>
@@ -1918,13 +1918,13 @@
         <v>36</v>
       </c>
       <c r="D39" s="2">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="E39" s="2">
         <v>1753</v>
       </c>
       <c r="F39" s="2">
-        <v>-1364</v>
+        <v>-1334</v>
       </c>
       <c r="G39" s="2">
         <v>15</v>
@@ -1936,7 +1936,7 @@
         <v>15</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>15</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D40" s="2">
-        <v>419</v>
+        <v>489</v>
       </c>
       <c r="E40" s="2">
         <v>1753</v>
       </c>
       <c r="F40" s="2">
-        <v>-1334</v>
+        <v>-1264</v>
       </c>
       <c r="G40" s="2">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>15</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>15</v>
@@ -1979,22 +1979,22 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D41" s="2">
-        <v>686</v>
+        <v>738</v>
       </c>
       <c r="E41" s="2">
         <v>1753</v>
       </c>
       <c r="F41" s="2">
-        <v>-1067</v>
+        <v>-1015</v>
       </c>
       <c r="G41" s="2">
         <v>30</v>
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>15</v>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>12</v>
@@ -2026,10 +2026,10 @@
         <v>419</v>
       </c>
       <c r="E42" s="2">
-        <v>1753</v>
+        <v>883</v>
       </c>
       <c r="F42" s="2">
-        <v>-1334</v>
+        <v>-464</v>
       </c>
       <c r="G42" s="2">
         <v>15</v>
@@ -2040,8 +2040,8 @@
       <c r="I42" s="2">
         <v>15</v>
       </c>
-      <c r="J42" s="4" t="s">
-        <v>21</v>
+      <c r="J42" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>15</v>
@@ -2049,22 +2049,22 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D43" s="2">
-        <v>684</v>
+        <v>614</v>
       </c>
       <c r="E43" s="2">
-        <v>1753</v>
+        <v>883</v>
       </c>
       <c r="F43" s="2">
-        <v>-1069</v>
+        <v>-269</v>
       </c>
       <c r="G43" s="2">
         <v>40</v>
@@ -2075,8 +2075,8 @@
       <c r="I43" s="2">
         <v>-10</v>
       </c>
-      <c r="J43" s="4" t="s">
-        <v>21</v>
+      <c r="J43" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>15</v>
@@ -2084,7 +2084,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>12</v>
@@ -2093,13 +2093,13 @@
         <v>19</v>
       </c>
       <c r="D44" s="2">
-        <v>738</v>
+        <v>626</v>
       </c>
       <c r="E44" s="2">
-        <v>1753</v>
+        <v>883</v>
       </c>
       <c r="F44" s="2">
-        <v>-1015</v>
+        <v>-257</v>
       </c>
       <c r="G44" s="2">
         <v>30</v>
@@ -2110,8 +2110,8 @@
       <c r="I44" s="2">
         <v>0</v>
       </c>
-      <c r="J44" s="4" t="s">
-        <v>21</v>
+      <c r="J44" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>15</v>
@@ -2119,22 +2119,22 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D45" s="2">
-        <v>419</v>
+        <v>369</v>
       </c>
       <c r="E45" s="2">
         <v>883</v>
       </c>
       <c r="F45" s="2">
-        <v>-464</v>
+        <v>-514</v>
       </c>
       <c r="G45" s="2">
         <v>15</v>
@@ -2145,8 +2145,8 @@
       <c r="I45" s="2">
         <v>15</v>
       </c>
-      <c r="J45" s="5" t="s">
-        <v>26</v>
+      <c r="J45" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>15</v>
@@ -2154,31 +2154,31 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D46" s="2">
-        <v>614</v>
+        <v>389</v>
       </c>
       <c r="E46" s="2">
         <v>883</v>
       </c>
       <c r="F46" s="2">
-        <v>-269</v>
+        <v>-494</v>
       </c>
       <c r="G46" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H46" s="2">
         <v>30</v>
       </c>
       <c r="I46" s="2">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>14</v>
@@ -2189,13 +2189,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D47" s="2">
         <v>626</v>
@@ -2215,115 +2215,10 @@
       <c r="I47" s="2">
         <v>0</v>
       </c>
-      <c r="J47" s="5" t="s">
-        <v>26</v>
+      <c r="J47" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48" s="2">
-        <v>389</v>
-      </c>
-      <c r="E48" s="2">
-        <v>883</v>
-      </c>
-      <c r="F48" s="2">
-        <v>-494</v>
-      </c>
-      <c r="G48" s="2">
-        <v>15</v>
-      </c>
-      <c r="H48" s="2">
-        <v>30</v>
-      </c>
-      <c r="I48" s="2">
-        <v>15</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D49" s="2">
-        <v>614</v>
-      </c>
-      <c r="E49" s="2">
-        <v>883</v>
-      </c>
-      <c r="F49" s="2">
-        <v>-269</v>
-      </c>
-      <c r="G49" s="2">
-        <v>40</v>
-      </c>
-      <c r="H49" s="2">
-        <v>30</v>
-      </c>
-      <c r="I49" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="2">
-        <v>626</v>
-      </c>
-      <c r="E50" s="2">
-        <v>883</v>
-      </c>
-      <c r="F50" s="2">
-        <v>-257</v>
-      </c>
-      <c r="G50" s="2">
-        <v>30</v>
-      </c>
-      <c r="H50" s="2">
-        <v>30</v>
-      </c>
-      <c r="I50" s="2">
-        <v>0</v>
-      </c>
-      <c r="J50" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K50" s="2" t="s">
         <v>15</v>
       </c>
     </row>
